--- a/論文/資料/資料集分佈_20260921-67.xlsx
+++ b/論文/資料/資料集分佈_20260921-67.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\winky\Desktop\code\論文\資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1A06D2-295F-4ED7-84D2-F82BEBFC932A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F277C3-F7DC-4096-93C6-2A838D60B5E7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7530" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="牙位x性別" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,14 @@
     <sheet name="年齡x性別" sheetId="3" r:id="rId3"/>
     <sheet name="說明" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <r>
       <rPr>
@@ -805,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -826,6 +832,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1876,6 +1885,252 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>性別</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4A18-476D-A3D9-527F2297533F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>實際長度x性別!$F$4:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>F</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>M</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>實際長度x性別!$F$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4A18-476D-A3D9-527F2297533F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -2452,6 +2707,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -3463,6 +3758,525 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4041,6 +4855,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>478972</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>168733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>304801</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>136076</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA9521EE-F0A6-45E3-BCFC-9C97EC38E45C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4270,13 +5120,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5">
+    <row r="1" spans="1:4" ht="16.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4447,24 +5297,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5">
+    <row r="1" spans="1:7" ht="16.8">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -4477,8 +5327,14 @@
       <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -4492,8 +5348,14 @@
         <f t="shared" ref="D5:D13" si="0">SUM(B5:C5)</f>
         <v>1</v>
       </c>
+      <c r="F5" s="6">
+        <v>40</v>
+      </c>
+      <c r="G5" s="6">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -4507,8 +5369,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
@@ -4522,8 +5386,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:7">
       <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
@@ -4537,8 +5403,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:7">
       <c r="A9" s="5" t="s">
         <v>21</v>
       </c>
@@ -4552,8 +5420,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -4567,8 +5437,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:7">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -4582,8 +5454,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -4597,8 +5471,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:7">
       <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
@@ -4612,8 +5488,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
         <v>5</v>
       </c>
@@ -4629,6 +5507,8 @@
         <f>SUM(D5:D13)</f>
         <v>67</v>
       </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -4641,13 +5521,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5">
+    <row r="1" spans="1:4" ht="16.8">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -4804,7 +5684,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
